--- a/data/output/evaluasi_95.xlsx
+++ b/data/output/evaluasi_95.xlsx
@@ -9,9 +9,9 @@
   <sheets>
     <sheet name="9500" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="9501" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="9502" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="9503" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="9504" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="9504" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="9502" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="9503" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -475,20 +475,20 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>5.950286807406135</v>
+        <v>5.228285699718463</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>adhb_net_ekspor_q1-25</t>
+          <t>adhb_pkp_q3-25</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Diskrepansi lebih dari +- 5 persen</t>
+          <t>Diskrepansi ADHB antara Provinsi dan total Kabupaten/Kota lebih dari (+-5%)</t>
         </is>
       </c>
     </row>
@@ -503,20 +503,20 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-0.7144308730876187</v>
+        <v>69.13463049945857</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>q-to-q_pkrt_q1-25 vs q-to-q_pkrt_q1-25.1</t>
+          <t>adhb_pi_q3-25</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Growth lebih dari +- 2 kalinya</t>
+          <t>Diskrepansi ADHB antara Provinsi dan total Kabupaten/Kota lebih dari (+-5%)</t>
         </is>
       </c>
     </row>
@@ -531,20 +531,20 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>q2-25</t>
+          <t>q1-25</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.7054198603906128</v>
+        <v>6.048616708911553</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>q-to-q_pklnprt_q2-25 vs q-to-q_pklnprt_q2-25.1</t>
+          <t>adhb_net_ekspor_q1-25</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Growth lebih dari +- 2 kalinya</t>
+          <t>Diskrepansi ADHB antara Provinsi dan total Kabupaten/Kota lebih dari (+-5%)</t>
         </is>
       </c>
     </row>
@@ -559,20 +559,20 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q2-25</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.5813455843185907</v>
+        <v>6.705992984670854</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>implisit_q-to-q_pmtb_q1-25 vs implisit_q-to-q_pmtb_q1-25.1</t>
+          <t>adhb_net_ekspor_q2-25</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Growth lebih dari +- 2 kalinya</t>
+          <t>Diskrepansi ADHB antara Provinsi dan total Kabupaten/Kota lebih dari (+-5%)</t>
         </is>
       </c>
     </row>
@@ -587,20 +587,580 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>17.33290624919632</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>adhb_net_ekspor_q3-25</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Diskrepansi ADHB antara Provinsi dan total Kabupaten/Kota lebih dari (+-5%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>95</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Papua Selatan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>8.400434728402635</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>adhk_pi_q3-25</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Diskrepansi ADHK antara Provinsi dan total Kabupaten/Kota lebih dari (+-5%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>95</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Papua Selatan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>7.02364319815856</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>adhk_net_ekspor_q3-25</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Diskrepansi ADHK antara Provinsi dan total Kabupaten/Kota lebih dari (+-5%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>95</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Papua Selatan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>-31.32549600306655</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>distribusi_net_ekspor_q3-25 vs distribusi_net_ekspor_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Diskrepansi Distribusi antara Provinsi dan total Kabupaten/Kota lebih dari (+-5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>95</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Papua Selatan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>2.249700459127014</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>q-to-q_pkrt_q2-25 vs q-to-q_pkrt_q2-25.1</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>95</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Papua Selatan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>0.9633567468491887</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>q-to-q_pkrt_q3-25 vs q-to-q_pkrt_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>95</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Papua Selatan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
           <t>q1-25</t>
         </is>
       </c>
-      <c r="D6" t="n">
-        <v>1.023948123618682</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>implisit_y-on-y_pklnprt_q1-25 vs implisit_y-on-y_pklnprt_q1-25.1</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Growth lebih dari +- 2 kalinya</t>
+      <c r="D12" t="n">
+        <v>-19.44136881869851</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q1-25 vs q-to-q_pkp_q1-25.1</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>95</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Papua Selatan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>2.525015305516467</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q2-25 vs q-to-q_pkp_q2-25.1</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>95</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Papua Selatan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>8.341544761441272</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q3-25 vs q-to-q_pkp_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>95</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Papua Selatan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>-9.645605844247617</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q1-25 vs q-to-q_pmtb_q1-25.1</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>95</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Papua Selatan</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>3.427555791062598</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>y-on-y_pdrb_q1-25 vs y-on-y_pdrb_q1-25.1</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,3 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>95</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Papua Selatan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>4.082025188409502</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>y-on-y_pdrb_q3-25 vs y-on-y_pdrb_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,01 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>95</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Papua Selatan</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>4.330153044891919</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>y-on-y_pkrt_q3-25 vs y-on-y_pkrt_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,05 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>95</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Papua Selatan</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>-2.704893217414807</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q1-25 vs y-on-y_pkp_q1-25.1</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>95</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Papua Selatan</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>1.368755936865421</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q3-25 vs y-on-y_pkp_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,05 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>95</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Papua Selatan</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>3.427555791062598</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>c-to-c_pdrb_q1-25 vs c-to-c_pdrb_q1-25.1</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,3 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>95</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Papua Selatan</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>-2.704893217414807</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q1-25 vs c-to-c_pkp_q1-25.1</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>95</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Papua Selatan</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>-0.5984923545433184</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q3-25 vs c-to-c_pkp_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Nilai antara Provinsi dan total Kabupaten/Kota beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>95</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Papua Selatan</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>2.035167425403716</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkrt_q2-25 vs implisit_q-to-q_pkrt_q2-25.1</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Diskrepansi Implisit Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>95</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Papua Selatan</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>0.7894916783168634</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkrt_q3-25 vs implisit_q-to-q_pkrt_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Diskrepansi Implisit Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>95</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Papua Selatan</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>5.003920458086046</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkrt_q3-25 vs implisit_y-on-y_pkrt_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
         </is>
       </c>
     </row>
@@ -615,7 +1175,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -665,16 +1225,16 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>160572.6488847876</v>
+        <v>3.058157952487654</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>adhb_pi_q1-25_ril vs adhb_pi_q1-25_rev</t>
+          <t>sog_q_pi_q1-25_ril vs sog_q_pi_q1-25_rev</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Angka revisi lebih dari +- 10 persen</t>
+          <t>SoG PI lebih dari +-2 persen</t>
         </is>
       </c>
     </row>
@@ -689,20 +1249,20 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q2-25</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>95215.76771867572</v>
+        <v>-2.603756462308382</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>adhk_pi_q1-25_ril vs adhk_pi_q1-25_rev</t>
+          <t>sog_q_pi_q2-25_ril vs sog_q_pi_q2-25_rev</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Angka revisi lebih dari +- 10 persen</t>
+          <t>SoG PI lebih dari +-2 persen</t>
         </is>
       </c>
     </row>
@@ -721,16 +1281,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-3.669010474416085</v>
+        <v>7.356791633881239</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>q-to-q_pklnprt_q1-25_ril vs q-to-q_pklnprt_q1-25_rev</t>
+          <t>sog_y-on-y_pi_q1-25_ril vs sog_y-on-y_pi_q1-25_rev</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>SoG PI lebih dari +-2 persen</t>
         </is>
       </c>
     </row>
@@ -745,76 +1305,20 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1.695578931657433</v>
+        <v>-0.8004665272955529</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>implisit_q-to-q_pklnprt_q1-25_ril vs implisit_q-to-q_pklnprt_q1-25_rev</t>
+          <t>c-to-c_pkp_q3-25_prov vs c-to-c_pkp_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>9501</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Kabupaten Merauke</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>q1-25</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>0.9445006842320479</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>implisit_y-on-y_pklnprt_q1-25_ril vs implisit_y-on-y_pklnprt_q1-25_rev</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>9501</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Kabupaten Merauke</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>q1-25</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>-0.05093575308550934</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>sog_q_pklnprt_q1-25_ril vs sog_q_pklnprt_q1-25_rev</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -829,7 +1333,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -866,39 +1370,39 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>9502</v>
+        <v>9504</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Kabupaten Boven Digoel</t>
+          <t>Kabupaten Asmat</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q2-25</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>13311.68</v>
+        <v>2.48888038865804</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>adhb_pi_q1-25_ril vs adhb_pi_q1-25_rev</t>
+          <t>sog_q_pi_q2-25_ril vs sog_q_pi_q2-25_rev</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Angka revisi lebih dari +- 10 persen</t>
+          <t>SoG PI lebih dari +-2 persen</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>9502</v>
+        <v>9504</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Kabupaten Boven Digoel</t>
+          <t>Kabupaten Asmat</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -907,44 +1411,240 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>7660.603374361484</v>
+        <v>4.022727209731381</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>adhk_pi_q1-25_ril vs adhk_pi_q1-25_rev</t>
+          <t>sog_y-on-y_pi_q1-25_ril vs sog_y-on-y_pi_q1-25_rev</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Angka revisi lebih dari +- 10 persen</t>
+          <t>SoG PI lebih dari +-2 persen</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>9502</v>
+        <v>9504</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Kabupaten Boven Digoel</t>
+          <t>Kabupaten Asmat</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.7410997070330655</v>
+        <v>-2.250675463426084</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>sog_q_pi_q1-25_ril vs sog_q_pi_q1-25_rev</t>
+          <t>q-to-q_pkrt_q3-25_prov vs q-to-q_pkrt_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>9504</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Asmat</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>0.1672363710242205</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q3-25_prov vs q-to-q_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>9504</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Asmat</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>-0.7958911891310647</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>9504</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Asmat</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>-0.2594899124440473</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q3-25_prov vs y-on-y_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>9504</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Asmat</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>-0.5819533844812397</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q3-25_prov vs c-to-c_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>9504</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Asmat</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>-0.9690481308690124</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkrt_q3-25_prov vs implisit_q-to-q_pkrt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9504</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Asmat</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>5.399644705556594</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>sog_q_pi_q3-25</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>9504</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Asmat</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>3.090738998579011</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>sog_y-on-y_pi_q3-25</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
         </is>
       </c>
     </row>
@@ -959,7 +1659,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -996,11 +1696,11 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>9503</v>
+        <v>9502</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Kabupaten Mappi</t>
+          <t>Kabupaten Boven Digoel</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1009,296 +1709,100 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-12327.6482456797</v>
+        <v>4.837313841194033</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>adhb_pi_q1-25_ril vs adhb_pi_q1-25_rev</t>
+          <t>sog_y-on-y_pi_q1-25_ril vs sog_y-on-y_pi_q1-25_rev</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Angka revisi lebih dari +- 10 persen</t>
+          <t>SoG PI lebih dari +-2 persen</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>9503</v>
+        <v>9502</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Kabupaten Mappi</t>
+          <t>Kabupaten Boven Digoel</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-7821.092135522184</v>
+        <v>3.41499971685635</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>adhk_pi_q1-25_ril vs adhk_pi_q1-25_rev</t>
+          <t>q-to-q_pkp_q3-25_prov vs q-to-q_pkp_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Angka revisi lebih dari +- 10 persen</t>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>9503</v>
+        <v>9502</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Kabupaten Mappi</t>
+          <t>Kabupaten Boven Digoel</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-4.194292650974516</v>
+        <v>-2.270551440197632</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>q-to-q_pklnprt_q1-25_ril vs q-to-q_pklnprt_q1-25_rev</t>
+          <t>c-to-c_pkp_q3-25_prov vs c-to-c_pkp_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>9503</v>
+        <v>9502</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Kabupaten Mappi</t>
+          <t>Kabupaten Boven Digoel</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-7.728744027750084</v>
+        <v>2.138288123086023</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>y-on-y_pklnprt_q1-25_ril vs y-on-y_pklnprt_q1-25_rev</t>
+          <t>sog_y-on-y_pi_q3-25</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>9503</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Kabupaten Mappi</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>q1-25</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>-7.728744027750084</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>c-to-c_pklnprt_q1-25_ril vs c-to-c_pklnprt_q1-25_rev</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>9503</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Kabupaten Mappi</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>q1-25</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>1.439101609584359</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>implisit_q-to-q_pklnprt_q1-25_ril vs implisit_q-to-q_pklnprt_q1-25_rev</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>9503</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Kabupaten Mappi</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>q1-25</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>1.317679767762193</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>implisit_y-on-y_pklnprt_q1-25_ril vs implisit_y-on-y_pklnprt_q1-25_rev</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>9503</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Kabupaten Mappi</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>q1-25</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>-0.08119085421107267</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>sog_q_pklnprt_q1-25_ril vs sog_q_pklnprt_q1-25_rev</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>9503</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Kabupaten Mappi</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>q1-25</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>-1.184859165175672</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>sog_q_pi_q1-25_ril vs sog_q_pi_q1-25_rev</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>9503</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Kabupaten Mappi</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>q1-25</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>-0.1553778263482614</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>sog_y-on-y_pklnprt_q1-25_ril vs sog_y-on-y_pklnprt_q1-25_rev</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>9503</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Kabupaten Mappi</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>q1-25</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>0.3687675645817424</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>sog_y-on-y_pi_q1-25_ril vs sog_y-on-y_pi_q1-25_rev</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Growth revisi berlawanan arah</t>
+          <t>SoG PI lebih dari +-2 persen</t>
         </is>
       </c>
     </row>
@@ -1313,7 +1817,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1350,29 +1854,113 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>9504</v>
+        <v>9503</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Kabupaten Asmat</t>
+          <t>Kabupaten Mappi</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1.949010072025571</v>
+        <v>-0.5077173478849402</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>implisit_y-on-y_pkp_q1-25_ril vs implisit_y-on-y_pkp_q1-25_rev</t>
+          <t>q-to-q_pkrt_q3-25_prov vs q-to-q_pkrt_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>9503</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Mappi</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>3.182639157084018</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q3-25_prov vs q-to-q_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>9503</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Mappi</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>-5.934393423782388</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>sog_q_pi_q3-25</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>9503</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Mappi</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>-6.444134628361707</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>sog_y-on-y_pi_q3-25</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
         </is>
       </c>
     </row>

--- a/data/output/evaluasi_95.xlsx
+++ b/data/output/evaluasi_95.xlsx
@@ -712,7 +712,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -768,7 +768,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -796,7 +796,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -824,7 +824,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -852,7 +852,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -880,7 +880,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,3 point)</t>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
         </is>
       </c>
     </row>
@@ -936,7 +936,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,05 point)</t>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
         </is>
       </c>
     </row>
@@ -964,7 +964,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -992,7 +992,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,05 point)</t>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
         </is>
       </c>
     </row>
@@ -1020,7 +1020,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,3 point)</t>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
         </is>
       </c>
     </row>
@@ -1048,7 +1048,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -1160,7 +1160,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
